--- a/output/customers_Vive_Living.xlsx
+++ b/output/customers_Vive_Living.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,7068 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>573128530946</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Henderson J</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Berrios Olivera</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>573122132304</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Arango Ossa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>573113154911</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jesus Arbey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gaviria Hernandez</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>573223364203</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Garzón</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>573045247486</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Otero</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>573183644257</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Angel Alfonso</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ramirez Díaz</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>573013103545</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rubiela</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>573015986977</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>573144435695</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Oswaldo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ome</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>573001234567</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ramirez Atehortúa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>573136151713</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Flavio</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Moreno</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>573146177060</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>573123971509</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bocanegra</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>573045854060</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Julian Esteban</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hincapie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>573174029325</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Natalia Maria</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Abdala Gonzalez</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>573213833904</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Erika J</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Álvarez</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>573188153484</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Willyam Leonardo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alcalá Quijano</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>573006469858</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Serna</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>573171609587</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cecilia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Malaver</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>573008364862</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cadavid</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>573128918774</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yesid</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>573173771222</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>573013714710</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>573234957304</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yuliana Maria</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ayala Lopez</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>573148825616</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yeye</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Naranjo</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>573001024011</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jhonatan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>573104504943</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Longa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>573137936576</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Johnathan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Manco Tobon</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>573183505414</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Luis Miguel</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bernal</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>573155049342</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>573006537888</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>573116002971</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oswaldo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>573246660029</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>573126438647</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Restrepo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>573124685782</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yuly</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>573188372111</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gerson Iván</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Duran</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>573017727937</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wilmar</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Perez</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>573223784677</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wilver Arley</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mosquera Vanegas</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>573026139975</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Parra</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>573209071682</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mejia</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>573127707349</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Paula Andrea Usuga</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Espinosa</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>573206888624</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mendez</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>573206956555</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gonzalo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Villa Villegas</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>573137802259</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Calle</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>573137317794</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>573104755972</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ingrid</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Barrera</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>573187903268</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Luis Alfonso</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Londoño Castaño</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>573017919626</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>573022574096</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jaime Rafael Guerrero</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Garcia</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>573015254631</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Zambrano</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>573117250924</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>573143941415</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jose German</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cardenas Cruz</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>573116130678</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Zapata</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>573023851422</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Montaño Parra</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>573117410376</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Alejo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Arboleda</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>573006859228</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Melani Gisella</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Viveros Morenos</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>573148300224</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Lopera Velez</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>573108374163</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Mejia</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>573118445692</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Luis Alberto</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Herrera</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>573148183788</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cano</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>573244812072</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jesus Gallardo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Mejia</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>573006526152</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Alzate</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>573137447977</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Arles</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Restrepo</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>573128325777</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Duvian</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Castano</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>573112270807</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Duque</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>573113798244</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sebastian Escobar</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Freydell</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>573124147943</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mj-tech</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Serna Blandon</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>573133611464</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Lasso Arias</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>573014362120</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Saul Antonio</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chico Torres</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>573103724743</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Gutierrez Rivas</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>573016623669</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Simón Álvarez</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Villegas</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>573003033435</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>573122655340</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lina María</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Roldán Botero</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>573017843743</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jiménez</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>573103896426</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Acosta</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>573504401811</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Vélez</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>573006516157</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Escobar Vélez</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>573163325432</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Paola Andrea</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Patiño</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>573132686243</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Becerra</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>573508142748</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Edwin G.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Montoya Hoyos</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>573103989148</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sánchez</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>573143930714</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jorge L</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Gaviria</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>573013991671</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Eduar</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Matiz</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>573505801880</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Víctor Manuel</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cortes Santos</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>573017566143</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Vargas</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>573007805847</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hincapi</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>573117617952</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Carloa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Segura</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>573202357808</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gloria Isabel</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Daza</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>573144583611</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Patiño</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>573148976675</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Alvaro</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Moreno</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>573104249325</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Luis German</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fajardo</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>573017527438</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mejia Gomez</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>573012852701</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Luis Felipe</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Espinal</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>573113208654</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Vlez</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>573161885979</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lovera</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>573117628969</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Orozco</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>573173722491</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Wilmar</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>573024017303</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>573007368015</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Fabian Esteban</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Herrera Herrera</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>573183244600</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>John Fredy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Salazar Arredondo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>573146184110</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Andres</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Rios</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>573233051107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>573174245213</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Luis Gonzaga</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Marin Osorio</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>573145221590</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Agustín</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Vélez</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>573164702242</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Bayron</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Saldarriaga</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>573013176944</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gil</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>573207003332</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>573104265819</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Álvaro</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Gómez Fernández</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>573204116132</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>573144179796</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>573174144706</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Elver</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>573166923170</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Villa</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>573057514682</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Montoya</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>573167036258</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Marcial</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mueses</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>573207248168</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Luz Mila</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Echavarria</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>573107176499</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Víctor Manuel</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Turpin Martinez</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>573043761062</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ana Dely</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Espinosa Montoya</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>573184472310</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>José Fernando</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tobías</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>573013382948</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Botia</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>573014390808</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Quiintero</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>573225235334</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hernando</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Mejia Restrepo</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>573006977846</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Gutierrez Giraldo</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>573008375110</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Mariano</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hernández Camargo</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>573187169190</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ismael</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Restrepo Correa</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>573156658887</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Carlos Manuel</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Uribe</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>573506135023</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jose Alejandro</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Zuluaga Salazar</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>573006086033</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Victor Eduardo</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Gutierrez Garcia</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>573504210957</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hector Andres</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Pelaez</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>573014319008</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Alejo</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pérez</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>573116753594</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Walter</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Gómez</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>573147916271</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Maria Paula</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Rincón Castaño</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>573157794665</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Maria V</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>573206811952</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Carlos Andrés Palacios Agudelo</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Palacio Agudelo</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>573004459271</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Gómez Buitrago</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>573137885296</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Agámez Marchena</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>573133096818</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Margarita</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>573004943764</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Katherinne</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Gallego</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>573052764205</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Julio Cesar</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Gutierrez Fonseca</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>573226674165</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Manuel José</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Urueta</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>573014715339</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Grajales Rua</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>573108467896</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>573146815005</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Cecilia Restrepo Alvarez</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>573133778218</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Rodriguez Zamora</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>573016741340</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Franco Andres</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pantoja Santacruz</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>573002208793</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Trujillo</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>573009590991</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Luzedi</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Garciagarcia</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>573003489154</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Juan Felipe</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Velez Alvarez</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>573189225888</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Filadelfo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Loboa Caicedo</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>573124500902</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Juan Pablo</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Gómez Escorcia</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>573052200111</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>573148813835</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Cerli Mildrey</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Hoyos Gomez</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>573163682075</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ivon</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>573008163481</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>María</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Rendon</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>573163540405</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mario Pérez</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>573218339208</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Federico</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Suescún Bedoya</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>573147730003</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Juan David</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Cardeño Rengifo</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>573143440006</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Antonio José</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Contreras</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>573103951864</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Mauricio</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Bohorquez Orozco</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>573212070244</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Javier Mauricio</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Hernández Castro</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>573043652040</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>573217511620</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>D. Arboleda</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>573168326002</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Andrés</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Zuluaga</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>573228195106</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jorge Armando</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Gallego Diaz</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>573108329228</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>John Jairo</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Uribe</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>573136569673</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Henao</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>573183001456</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Luis Vasquez Hipnoterapeuta Y Coach En</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Pnl</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>573024709790</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tomás Moncada</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>573043460864</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Martinez Agudelo</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>573147303372</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Serna</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>573187436101</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Raymond</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Rubin</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>573117194474</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Uriana</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>573103258382</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>573012751512</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Pareja</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>573164421499</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>573001119374</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Hoyos</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>573046689664</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>573122278261</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Escobar</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>573016091192</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Jonathan Andres</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Rua Penagos</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>573102027190</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Almanza</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>573108287526</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Jesús</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Velasquez Giraldo</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>573006134560</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Jorge René</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Estupiñán Guzmán</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>573013452168</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Elena Beatriz</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>De La Hoz Osorio</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>573005766167</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Pineda Arango</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>573002394302</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Hinestrosa</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>573007041014</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Santa</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>573174275983</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Fabio</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ruiz Galeano</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>573155100153</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Delgado Restrepo</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>573124577943</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Guillermo</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>573108253701</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Gladimir</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Zanoja</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>573008057436</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Jose Jaime</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Cifuentes Gonzalez</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>573156363636</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Lozano</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>573006108484</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Luis Alejandro</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Guzmán Gomez</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>573011208076</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Delio</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Salgdo</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>573103613806</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Mesa Martínez</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>573128721411</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Rodríguez</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>573507270670</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Juan Angel</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Soto Aristizabal</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>573163447986</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Velasquez</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>573185233450</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ana Beatriz</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Agudelo Vélez</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>573209188950</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sandra Patricia</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>León Cruz</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>573155683910</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Beatriz Helena</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Patiño Avendaño</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>573116351670</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Leon Augusto</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Martínez Giraldo</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>573117643335</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Carlos Alberto</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Calle Echavarria</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>573016689903</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Marta Cecilia</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Rivas Durango</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>573002492198</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>573003067061</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>573122773145</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Johanna Marcela</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fernández Echeverri</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>573167886774</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>José Nelson</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Cicery</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>573016592548</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Jorge Eduardo</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Jimenez Castañeda</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>573128347587</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Iván Darío</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Salamanca Castro</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>573013377320</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Adriana Patricia</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sanchez Alvarez</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>573116094724</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Delgado</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>573222516049</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Cesar Fernando</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Rojas Guevara</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>573003081235</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>573017074390</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Jiménez</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>573128033653</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Aima Valentina</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Arias Perez</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>573046568885</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Salinas</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>573016154557</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Dr. Oscar</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Aristizabal</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>573104597427</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Serna</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>573163430459</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Andres Cardona</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>573007866912</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Fabian Andres</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Callejas Varela</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>573122886556</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Miranda</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>573007246984</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Florez Urrego</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>573183350774</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Cañón</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>573192341100</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Osorio Tamayo</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>573176408056</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>573180278436</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Ceballos</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>573124754275</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Felipe Garzón</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Cristancho</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>573008784196</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Arias</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>573013571001</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Eduardo Arias Cadavid</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Arias Cadavid</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>573126496480</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Zuñiga</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>573137626474</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Karina</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Cardona</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>573124860471</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Esteban Bautista</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Clavijo</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>573222150910</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Johanna</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Torres</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>573218605452</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Bohórquez</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>573045380402</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Cristian Camilo</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>573207101870</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Restrepo</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>573204543149</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Salas</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>573014716531</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Dra. Viviana Cortes</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>573147712566</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Alejandra Marcela</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Garcia Rios</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>573137826254</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Dora</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Cecilia Perez Pulgarin</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>573103876683</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Fabricio Concejal</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>573175195405</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Fundacion</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>573206054434</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Yazmin</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sucerquia</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>573008165001</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Liliana</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Cabrales</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>573016425381</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Enith Teresa</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Pasos</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>573103946588</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>573212161668</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Giovanni</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Salas Araque</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>573104272021</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mara Camila</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Chaparro</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>573104625410</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Blanca</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Zapata</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>573136588384</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Juliana</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Morales Cañón</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>573122860109</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Plazas Sanchez</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>573164601889</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Agudelo</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>573217519687</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Gustavo</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Adolfo Santa</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>573104360382</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Ruben</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Medina</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>573118539115</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Puello</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>573186496232</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Pili</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Gutiérrez</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>573188363997</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Castillo</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>573016756082</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Eliana</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bedoya</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>573007818092</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Juan Carlos</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Escobar</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>573008822373</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Daniel Jose</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Rudas</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>573102465436</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Yamile Chica</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>573013968367</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Natalia Gallego</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Vallejo</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>573146309255</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Maria Paulina</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Perez Sierra</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>573117624362</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>María Elena</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Yepes</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>573116306422</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lina Maria</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Pérez Uribe</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>573148290668</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Katherine Trespalacios</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>573136607972</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Jacobo</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Maya G</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>573135899407</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Joaquin</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Rivera Caro</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>573177831322</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Zapata</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>573007971530</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Marta</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Rios</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>573167409085</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Nury Johana</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Sandoval</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>573137484026</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>573104061112</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Alexandra Grisales Vahos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Alexandra Grisales Vahos</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>573113926575</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Remberto Luis</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Rhenals Garrido</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>573202360088</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Gaviria</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>573218171735</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ángel</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>573214383059</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Maria Alexandra</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ayala Lopez</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>573104382627</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Arango</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>573053696055</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Campos</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>573161347211</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Sergio Andrés</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Vásquez Rodriguez</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>573128166669</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Quintero Duque</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>573017957102</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Juanes</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Restrepo</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>573044613245</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>573153262401</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Natalia Andrea</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Muñoz Valero</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>573128952007</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>David Llano</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Cortes</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>573128869333</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Machado Román</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>573023657210</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Daniela</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Flórez</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>573193526430</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Andres Felipe</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Palacio Montoya</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>573007782877</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Jesus David</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Ramirez Sanchez</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>573203425658</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>573114079721</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Castano</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>573017853959</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Suarez Triana</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>573044383282</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Ocampo</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>573173093693</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Yaky</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ramírez Villegas</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>573126752038</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Isaias</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Barrios</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>573122705926</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Laura Giraldo</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Sarasa</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>573004328277</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Meneses</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>573007639972</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Angie Tatiana</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Escobar Franco</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>573206043216</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Naranjo Pizano</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>573012404261</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Arboleda</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>573133863170</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Flórez</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>573222168902</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lina</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Barrera</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>573104435563</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Alba</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>573105481020</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Luis Orlando</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Yepes Tabares</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>573104477331</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ana Maria</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Álvarez Restrepo</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>573132550308</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Payares</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>573137370103</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Jaramillo</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>573122063372</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Shirley Johana</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Munera Rua</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>573108483363</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Ana Maria</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Alvarez Fernandez</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>573122178530</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Camila</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Bedoya</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>573148889243</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Florez Garcia</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>573146152218</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Marchese</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>573144580632</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Laura Mercadeo</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Prueba Aguilar</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>573135748341</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Pabon</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>573043460864</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>573124457430</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Or.mm</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>573127938080</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>De La Hoz</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>573187620912</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Rios</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>573205309193</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Álvaro Fernando</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Portilla Araujo</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>573006545177</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Arango</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>573116204753</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Juanjose Galvis</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>VIVE LIVING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/customers_Vive_Living.xlsx
+++ b/output/customers_Vive_Living.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E322"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7354,17 +7354,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>573043460864</t>
+          <t>573124457430</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Or.mm</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -7376,17 +7376,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>573124457430</t>
+          <t>573127938080</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Or.mm</t>
+          <t>De La Hoz</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -7398,17 +7398,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>573127938080</t>
+          <t>573187620912</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Cielo</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>De La Hoz</t>
+          <t>Rios</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -7420,17 +7420,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>573187620912</t>
+          <t>573205309193</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>Álvaro Fernando</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Rios</t>
+          <t>Portilla Araujo</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -7442,17 +7442,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>573205309193</t>
+          <t>573006545177</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Álvaro Fernando</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Portilla Araujo</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -7464,42 +7464,20 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>573006545177</t>
+          <t>573116204753</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Juanjose Galvis</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>González</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>573116204753</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Juanjose Galvis</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>González</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
         <is>
           <t>VIVE LIVING</t>
         </is>

--- a/output/customers_Vive_Living.xlsx
+++ b/output/customers_Vive_Living.xlsx
@@ -459,10 +459,8 @@
           <t>Berrios Olivera</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E2" t="n">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -481,10 +479,8 @@
           <t>Arango Ossa</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -503,10 +499,8 @@
           <t>Gaviria Hernandez</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -525,10 +519,8 @@
           <t>Garzón</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -547,10 +539,8 @@
           <t>Otero</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -569,10 +559,8 @@
           <t>Ramirez Díaz</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -591,10 +579,8 @@
           <t>Molina</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -613,10 +599,8 @@
           <t>Medina</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -635,10 +619,8 @@
           <t>Ome</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -657,10 +639,8 @@
           <t>Ramirez Atehortúa</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -679,10 +659,8 @@
           <t>Moreno</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -701,10 +679,8 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -723,10 +699,8 @@
           <t>Bocanegra</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -745,10 +719,8 @@
           <t>Hincapie</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -767,10 +739,8 @@
           <t>Abdala Gonzalez</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -789,10 +759,8 @@
           <t>Álvarez</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -811,10 +779,8 @@
           <t>Alcalá Quijano</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -833,10 +799,8 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -855,10 +819,8 @@
           <t>Malaver</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -877,10 +839,8 @@
           <t>Cadavid</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -899,10 +859,8 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -921,10 +879,8 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -943,10 +899,8 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -965,10 +919,8 @@
           <t>Ayala Lopez</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -987,10 +939,8 @@
           <t>Naranjo</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1009,10 +959,8 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1031,10 +979,8 @@
           <t>Longa</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1053,10 +999,8 @@
           <t>Manco Tobon</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1075,10 +1019,8 @@
           <t>Bernal</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1097,10 +1039,8 @@
           <t>Mora</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1119,10 +1059,8 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1143,7 +1081,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -1163,10 +1101,8 @@
           <t>Morales</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1185,10 +1121,8 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1207,10 +1141,8 @@
           <t>Marcela</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1229,10 +1161,8 @@
           <t>Duran</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1251,10 +1181,8 @@
           <t>Perez</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1273,10 +1201,8 @@
           <t>Mosquera Vanegas</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1295,10 +1221,8 @@
           <t>Parra</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1317,10 +1241,8 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1339,10 +1261,8 @@
           <t>Espinosa</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1361,10 +1281,8 @@
           <t>Mendez</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -1383,10 +1301,8 @@
           <t>Villa Villegas</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -1405,10 +1321,8 @@
           <t>Calle</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1427,10 +1341,8 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1449,10 +1361,8 @@
           <t>Barrera</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1471,10 +1381,8 @@
           <t>Londoño Castaño</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1493,10 +1401,8 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -1515,10 +1421,8 @@
           <t>Garcia</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1537,10 +1441,8 @@
           <t>Zambrano</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1559,10 +1461,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1581,10 +1481,8 @@
           <t>Cardenas Cruz</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -1603,10 +1501,8 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -1625,10 +1521,8 @@
           <t>Montaño Parra</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -1647,10 +1541,8 @@
           <t>Arboleda</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -1671,7 +1563,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -1691,10 +1583,8 @@
           <t>Lopera Velez</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1603,8 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -1735,10 +1623,8 @@
           <t>Herrera</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -1757,10 +1643,8 @@
           <t>Cano</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -1779,10 +1663,8 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E62" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -1803,7 +1685,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -1823,10 +1705,8 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E64" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -1845,10 +1725,8 @@
           <t>Castano</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E65" t="n">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -1867,10 +1745,8 @@
           <t>Duque</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E66" t="n">
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -1889,10 +1765,8 @@
           <t>Freydell</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E67" t="n">
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -1911,10 +1785,8 @@
           <t>Serna Blandon</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E68" t="n">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -1933,10 +1805,8 @@
           <t>Lasso Arias</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E69" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -1955,10 +1825,8 @@
           <t>Chico Torres</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E70" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -1977,10 +1845,8 @@
           <t>Gutierrez Rivas</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E71" t="n">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -1999,10 +1865,8 @@
           <t>Villegas</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E72" t="n">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -2021,10 +1885,8 @@
           <t>Bermudez</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E73" t="n">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -2043,10 +1905,8 @@
           <t>Roldán Botero</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E74" t="n">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -2065,10 +1925,8 @@
           <t>Jiménez</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E75" t="n">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -2087,10 +1945,8 @@
           <t>Acosta</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E76" t="n">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -2109,10 +1965,8 @@
           <t>Vélez</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E77" t="n">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -2131,10 +1985,8 @@
           <t>Escobar Vélez</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E78" t="n">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -2153,10 +2005,8 @@
           <t>Patiño</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E79" t="n">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2175,10 +2025,8 @@
           <t>Becerra</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E80" t="n">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2197,10 +2045,8 @@
           <t>Montoya Hoyos</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E81" t="n">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -2219,10 +2065,8 @@
           <t>Sánchez</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E82" t="n">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -2241,10 +2085,8 @@
           <t>Gaviria</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E83" t="n">
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -2263,10 +2105,8 @@
           <t>Matiz</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E84" t="n">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -2285,10 +2125,8 @@
           <t>Cortes Santos</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E85" t="n">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -2307,10 +2145,8 @@
           <t>Vargas</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E86" t="n">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -2329,10 +2165,8 @@
           <t>Hincapi</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E87" t="n">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -2351,10 +2185,8 @@
           <t>Segura</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E88" t="n">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -2373,10 +2205,8 @@
           <t>Daza</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E89" t="n">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -2395,10 +2225,8 @@
           <t>Patiño</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E90" t="n">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -2417,10 +2245,8 @@
           <t>Moreno</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E91" t="n">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -2439,10 +2265,8 @@
           <t>Fajardo</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E92" t="n">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -2461,10 +2285,8 @@
           <t>Mejia Gomez</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E93" t="n">
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -2483,10 +2305,8 @@
           <t>Espinal</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E94" t="n">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -2505,10 +2325,8 @@
           <t>Vlez</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E95" t="n">
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -2527,10 +2345,8 @@
           <t>Lovera</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E96" t="n">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -2549,10 +2365,8 @@
           <t>Orozco</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E97" t="n">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -2571,10 +2385,8 @@
           <t>Franco</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E98" t="n">
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -2593,10 +2405,8 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E99" t="n">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -2615,10 +2425,8 @@
           <t>Herrera Herrera</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E100" t="n">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -2637,10 +2445,8 @@
           <t>Salazar Arredondo</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E101" t="n">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -2659,10 +2465,8 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E102" t="n">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -2681,10 +2485,8 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E103" t="n">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -2703,10 +2505,8 @@
           <t>Marin Osorio</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E104" t="n">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -2725,10 +2525,8 @@
           <t>Vélez</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E105" t="n">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -2747,10 +2545,8 @@
           <t>Saldarriaga</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E106" t="n">
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -2769,10 +2565,8 @@
           <t>Gil</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E107" t="n">
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -2791,10 +2585,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E108" t="n">
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -2813,10 +2605,8 @@
           <t>Gómez Fernández</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E109" t="n">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -2835,10 +2625,8 @@
           <t>Alvarez</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E110" t="n">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -2857,10 +2645,8 @@
           <t>Quintero</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E111" t="n">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -2879,10 +2665,8 @@
           <t>Martinez</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E112" t="n">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -2901,10 +2685,8 @@
           <t>Villa</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E113" t="n">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -2923,10 +2705,8 @@
           <t>Montoya</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E114" t="n">
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -2945,10 +2725,8 @@
           <t>Mueses</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E115" t="n">
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -2967,10 +2745,8 @@
           <t>Echavarria</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E116" t="n">
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -2989,10 +2765,8 @@
           <t>Turpin Martinez</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E117" t="n">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -3011,10 +2785,8 @@
           <t>Espinosa Montoya</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E118" t="n">
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -3033,10 +2805,8 @@
           <t>Tobías</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E119" t="n">
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -3055,10 +2825,8 @@
           <t>Botia</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E120" t="n">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -3077,10 +2845,8 @@
           <t>Quiintero</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E121" t="n">
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -3099,10 +2865,8 @@
           <t>Mejia Restrepo</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E122" t="n">
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -3121,10 +2885,8 @@
           <t>Gutierrez Giraldo</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E123" t="n">
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -3143,10 +2905,8 @@
           <t>Hernández Camargo</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E124" t="n">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -3165,10 +2925,8 @@
           <t>Restrepo Correa</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E125" t="n">
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3187,10 +2945,8 @@
           <t>Uribe</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E126" t="n">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -3209,10 +2965,8 @@
           <t>Zuluaga Salazar</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E127" t="n">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -3231,10 +2985,8 @@
           <t>Gutierrez Garcia</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E128" t="n">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -3253,10 +3005,8 @@
           <t>Pelaez</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E129" t="n">
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -3275,10 +3025,8 @@
           <t>Pérez</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E130" t="n">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -3297,10 +3045,8 @@
           <t>Gómez</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E131" t="n">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -3319,10 +3065,8 @@
           <t>Rincón Castaño</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E132" t="n">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -3341,10 +3085,8 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E133" t="n">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -3363,10 +3105,8 @@
           <t>Palacio Agudelo</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E134" t="n">
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -3387,7 +3127,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -3407,10 +3147,8 @@
           <t>Agámez Marchena</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E136" t="n">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -3429,10 +3167,8 @@
           <t>Castro</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E137" t="n">
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -3451,10 +3187,8 @@
           <t>Gallego</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E138" t="n">
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -3473,10 +3207,8 @@
           <t>Gutierrez Fonseca</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E139" t="n">
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -3495,10 +3227,8 @@
           <t>Urueta</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E140" t="n">
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -3517,10 +3247,8 @@
           <t>Grajales Rua</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E141" t="n">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -3539,10 +3267,8 @@
           <t>Hernandez</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E142" t="n">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -3561,10 +3287,8 @@
           <t>Cecilia Restrepo Alvarez</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E143" t="n">
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -3583,10 +3307,8 @@
           <t>Rodriguez Zamora</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E144" t="n">
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -3605,10 +3327,8 @@
           <t>Pantoja Santacruz</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E145" t="n">
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -3627,10 +3347,8 @@
           <t>Trujillo</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E146" t="n">
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -3649,10 +3367,8 @@
           <t>Garciagarcia</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E147" t="n">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -3671,10 +3387,8 @@
           <t>Velez Alvarez</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E148" t="n">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -3693,10 +3407,8 @@
           <t>Loboa Caicedo</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E149" t="n">
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -3715,10 +3427,8 @@
           <t>Gómez Escorcia</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E150" t="n">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -3737,10 +3447,8 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E151" t="n">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -3759,10 +3467,8 @@
           <t>Hoyos Gomez</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E152" t="n">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -3781,10 +3487,8 @@
           <t>Gonzalez</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E153" t="n">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -3803,10 +3507,8 @@
           <t>Rendon</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E154" t="n">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -3825,10 +3527,8 @@
           <t>Mario Pérez</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E155" t="n">
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -3847,10 +3547,8 @@
           <t>Suescún Bedoya</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E156" t="n">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -3869,10 +3567,8 @@
           <t>Cardeño Rengifo</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E157" t="n">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -3891,10 +3587,8 @@
           <t>Contreras</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E158" t="n">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -3913,10 +3607,8 @@
           <t>Bohorquez Orozco</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E159" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -3935,10 +3627,8 @@
           <t>Hernández Castro</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E160" t="n">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -3957,10 +3647,8 @@
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E161" t="n">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -3979,10 +3667,8 @@
           <t>D. Arboleda</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E162" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -4001,10 +3687,8 @@
           <t>Zuluaga</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E163" t="n">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -4023,10 +3707,8 @@
           <t>Gallego Diaz</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E164" t="n">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -4045,10 +3727,8 @@
           <t>Uribe</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E165" t="n">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -4067,10 +3747,8 @@
           <t>Henao</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E166" t="n">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -4089,10 +3767,8 @@
           <t>Pnl</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E167" t="n">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -4111,10 +3787,8 @@
           <t>Mesa</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E168" t="n">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -4135,7 +3809,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -4155,10 +3829,8 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E170" t="n">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -4177,10 +3849,8 @@
           <t>Rubin</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E171" t="n">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -4199,10 +3869,8 @@
           <t>Uriana</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E172" t="n">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -4223,7 +3891,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -4243,10 +3911,8 @@
           <t>Pareja</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E174" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -4265,10 +3931,8 @@
           <t>Molina</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E175" t="n">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -4287,10 +3951,8 @@
           <t>Hoyos</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E176" t="n">
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -4309,10 +3971,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E177" t="n">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -4331,10 +3991,8 @@
           <t>Escobar</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E178" t="n">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -4353,10 +4011,8 @@
           <t>Rua Penagos</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E179" t="n">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -4375,10 +4031,8 @@
           <t>Almanza</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E180" t="n">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -4397,10 +4051,8 @@
           <t>Velasquez Giraldo</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E181" t="n">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -4421,7 +4073,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -4441,10 +4093,8 @@
           <t>De La Hoz Osorio</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E183" t="n">
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -4463,10 +4113,8 @@
           <t>Pineda Arango</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E184" t="n">
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -4485,10 +4133,8 @@
           <t>Hinestrosa</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E185" t="n">
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -4509,7 +4155,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -4529,10 +4175,8 @@
           <t>Ruiz Galeano</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E187" t="n">
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -4551,10 +4195,8 @@
           <t>Delgado Restrepo</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E188" t="n">
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -4573,10 +4215,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E189" t="n">
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -4595,10 +4235,8 @@
           <t>Zanoja</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E190" t="n">
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -4617,10 +4255,8 @@
           <t>Cifuentes Gonzalez</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E191" t="n">
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -4639,10 +4275,8 @@
           <t>Lozano</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E192" t="n">
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -4661,10 +4295,8 @@
           <t>Guzmán Gomez</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E193" t="n">
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -4683,10 +4315,8 @@
           <t>Salgdo</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E194" t="n">
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -4705,10 +4335,8 @@
           <t>Mesa Martínez</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E195" t="n">
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -4727,10 +4355,8 @@
           <t>Rodríguez</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E196" t="n">
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -4749,10 +4375,8 @@
           <t>Soto Aristizabal</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E197" t="n">
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -4771,10 +4395,8 @@
           <t>Velasquez</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E198" t="n">
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -4793,10 +4415,8 @@
           <t>Agudelo Vélez</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E199" t="n">
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -4815,10 +4435,8 @@
           <t>León Cruz</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E200" t="n">
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -4837,10 +4455,8 @@
           <t>Patiño Avendaño</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E201" t="n">
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -4859,10 +4475,8 @@
           <t>Martínez Giraldo</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E202" t="n">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -4881,10 +4495,8 @@
           <t>Calle Echavarria</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E203" t="n">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -4903,10 +4515,8 @@
           <t>Rivas Durango</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E204" t="n">
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -4925,10 +4535,8 @@
           <t>Cabrera</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E205" t="n">
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -4947,10 +4555,8 @@
           <t>Parada</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E206" t="n">
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -4969,10 +4575,8 @@
           <t>Fernández Echeverri</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E207" t="n">
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -4991,10 +4595,8 @@
           <t>Cicery</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E208" t="n">
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -5013,10 +4615,8 @@
           <t>Jimenez Castañeda</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E209" t="n">
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -5035,10 +4635,8 @@
           <t>Salamanca Castro</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E210" t="n">
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -5057,10 +4655,8 @@
           <t>Sanchez Alvarez</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E211" t="n">
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -5079,10 +4675,8 @@
           <t>Delgado</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E212" t="n">
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -5101,10 +4695,8 @@
           <t>Rojas Guevara</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E213" t="n">
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -5123,10 +4715,8 @@
           <t>Martinez</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E214" t="n">
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -5145,10 +4735,8 @@
           <t>Jiménez</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E215" t="n">
+        <v/>
       </c>
     </row>
     <row r="216">
@@ -5167,10 +4755,8 @@
           <t>Arias Perez</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E216" t="n">
+        <v/>
       </c>
     </row>
     <row r="217">
@@ -5189,10 +4775,8 @@
           <t>Salinas</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E217" t="n">
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -5211,10 +4795,8 @@
           <t>Aristizabal</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E218" t="n">
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -5233,10 +4815,8 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E219" t="n">
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -5255,10 +4835,8 @@
           <t>Andres Cardona</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E220" t="n">
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -5277,10 +4855,8 @@
           <t>Callejas Varela</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E221" t="n">
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -5299,10 +4875,8 @@
           <t>Miranda</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E222" t="n">
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -5321,10 +4895,8 @@
           <t>Florez Urrego</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E223" t="n">
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -5343,10 +4915,8 @@
           <t>Cañón</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E224" t="n">
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -5365,10 +4935,8 @@
           <t>Osorio Tamayo</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E225" t="n">
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -5387,10 +4955,8 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E226" t="n">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -5409,10 +4975,8 @@
           <t>Ceballos</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E227" t="n">
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -5431,10 +4995,8 @@
           <t>Cristancho</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E228" t="n">
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -5453,10 +5015,8 @@
           <t>Arias</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E229" t="n">
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -5475,10 +5035,8 @@
           <t>Arias Cadavid</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E230" t="n">
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -5497,10 +5055,8 @@
           <t>Zuñiga</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E231" t="n">
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -5519,10 +5075,8 @@
           <t>Cardona</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E232" t="n">
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -5541,10 +5095,8 @@
           <t>Clavijo</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E233" t="n">
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -5563,10 +5115,8 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E234" t="n">
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -5585,10 +5135,8 @@
           <t>Bohórquez</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E235" t="n">
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -5607,10 +5155,8 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E236" t="n">
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -5629,10 +5175,8 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E237" t="n">
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -5651,10 +5195,8 @@
           <t>Salas</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E238" t="n">
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -5673,10 +5215,8 @@
           <t>Franco</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E239" t="n">
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -5695,10 +5235,8 @@
           <t>Garcia Rios</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E240" t="n">
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -5717,10 +5255,8 @@
           <t>Cecilia Perez Pulgarin</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E241" t="n">
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -5739,10 +5275,8 @@
           <t>Fabricio Concejal</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E242" t="n">
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -5761,10 +5295,8 @@
           <t>Humana</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E243" t="n">
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -5783,10 +5315,8 @@
           <t>Sucerquia</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E244" t="n">
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -5805,10 +5335,8 @@
           <t>Cabrales</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E245" t="n">
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -5827,10 +5355,8 @@
           <t>Pasos</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E246" t="n">
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -5849,10 +5375,8 @@
           <t>González</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E247" t="n">
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -5871,10 +5395,8 @@
           <t>Salas Araque</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E248" t="n">
+        <v/>
       </c>
     </row>
     <row r="249">
@@ -5893,10 +5415,8 @@
           <t>Chaparro</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E249" t="n">
+        <v/>
       </c>
     </row>
     <row r="250">
@@ -5915,10 +5435,8 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E250" t="n">
+        <v/>
       </c>
     </row>
     <row r="251">
@@ -5937,10 +5455,8 @@
           <t>Morales Cañón</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E251" t="n">
+        <v/>
       </c>
     </row>
     <row r="252">
@@ -5959,10 +5475,8 @@
           <t>Plazas Sanchez</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E252" t="n">
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -5981,10 +5495,8 @@
           <t>Agudelo</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E253" t="n">
+        <v/>
       </c>
     </row>
     <row r="254">
@@ -6003,10 +5515,8 @@
           <t>Adolfo Santa</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E254" t="n">
+        <v/>
       </c>
     </row>
     <row r="255">
@@ -6025,10 +5535,8 @@
           <t>Medina</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E255" t="n">
+        <v/>
       </c>
     </row>
     <row r="256">
@@ -6047,10 +5555,8 @@
           <t>Puello</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E256" t="n">
+        <v/>
       </c>
     </row>
     <row r="257">
@@ -6069,10 +5575,8 @@
           <t>Gutiérrez</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E257" t="n">
+        <v/>
       </c>
     </row>
     <row r="258">
@@ -6091,10 +5595,8 @@
           <t>Castillo</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E258" t="n">
+        <v/>
       </c>
     </row>
     <row r="259">
@@ -6113,10 +5615,8 @@
           <t>Bedoya</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E259" t="n">
+        <v/>
       </c>
     </row>
     <row r="260">
@@ -6137,7 +5637,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -6157,10 +5657,8 @@
           <t>Rudas</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E261" t="n">
+        <v/>
       </c>
     </row>
     <row r="262">
@@ -6179,10 +5677,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E262" t="n">
+        <v/>
       </c>
     </row>
     <row r="263">
@@ -6201,10 +5697,8 @@
           <t>Vallejo</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E263" t="n">
+        <v/>
       </c>
     </row>
     <row r="264">
@@ -6223,10 +5717,8 @@
           <t>Perez Sierra</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E264" t="n">
+        <v/>
       </c>
     </row>
     <row r="265">
@@ -6245,10 +5737,8 @@
           <t>Yepes</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E265" t="n">
+        <v/>
       </c>
     </row>
     <row r="266">
@@ -6267,10 +5757,8 @@
           <t>Pérez Uribe</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E266" t="n">
+        <v/>
       </c>
     </row>
     <row r="267">
@@ -6291,7 +5779,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>VIVE LIVING</t>
+          <t>Antioquia</t>
         </is>
       </c>
     </row>
@@ -6311,10 +5799,8 @@
           <t>Maya G</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E268" t="n">
+        <v/>
       </c>
     </row>
     <row r="269">
@@ -6333,10 +5819,8 @@
           <t>Rivera Caro</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E269" t="n">
+        <v/>
       </c>
     </row>
     <row r="270">
@@ -6355,10 +5839,8 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E270" t="n">
+        <v/>
       </c>
     </row>
     <row r="271">
@@ -6377,10 +5859,8 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E271" t="n">
+        <v/>
       </c>
     </row>
     <row r="272">
@@ -6399,10 +5879,8 @@
           <t>Sandoval</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E272" t="n">
+        <v/>
       </c>
     </row>
     <row r="273">
@@ -6421,10 +5899,8 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E273" t="n">
+        <v/>
       </c>
     </row>
     <row r="274">
@@ -6443,10 +5919,8 @@
           <t>Alexandra Grisales Vahos</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E274" t="n">
+        <v/>
       </c>
     </row>
     <row r="275">
@@ -6465,10 +5939,8 @@
           <t>Rhenals Garrido</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E275" t="n">
+        <v/>
       </c>
     </row>
     <row r="276">
@@ -6487,10 +5959,8 @@
           <t>Gaviria</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E276" t="n">
+        <v/>
       </c>
     </row>
     <row r="277">
@@ -6509,10 +5979,8 @@
           <t>Ángel</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E277" t="n">
+        <v/>
       </c>
     </row>
     <row r="278">
@@ -6531,10 +5999,8 @@
           <t>Ayala Lopez</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E278" t="n">
+        <v/>
       </c>
     </row>
     <row r="279">
@@ -6553,10 +6019,8 @@
           <t>Arango</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E279" t="n">
+        <v/>
       </c>
     </row>
     <row r="280">
@@ -6575,10 +6039,8 @@
           <t>Campos</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E280" t="n">
+        <v/>
       </c>
     </row>
     <row r="281">
@@ -6597,10 +6059,8 @@
           <t>Vásquez Rodriguez</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E281" t="n">
+        <v/>
       </c>
     </row>
     <row r="282">
@@ -6619,10 +6079,8 @@
           <t>Quintero Duque</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E282" t="n">
+        <v/>
       </c>
     </row>
     <row r="283">
@@ -6641,10 +6099,8 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E283" t="n">
+        <v/>
       </c>
     </row>
     <row r="284">
@@ -6663,10 +6119,8 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E284" t="n">
+        <v/>
       </c>
     </row>
     <row r="285">
@@ -6685,10 +6139,8 @@
           <t>Muñoz Valero</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E285" t="n">
+        <v/>
       </c>
     </row>
     <row r="286">
@@ -6707,10 +6159,8 @@
           <t>Cortes</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E286" t="n">
+        <v/>
       </c>
     </row>
     <row r="287">
@@ -6729,10 +6179,8 @@
           <t>Machado Román</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E287" t="n">
+        <v/>
       </c>
     </row>
     <row r="288">
@@ -6751,10 +6199,8 @@
           <t>Flórez</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E288" t="n">
+        <v/>
       </c>
     </row>
     <row r="289">
@@ -6773,10 +6219,8 @@
           <t>Palacio Montoya</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E289" t="n">
+        <v/>
       </c>
     </row>
     <row r="290">
@@ -6795,10 +6239,8 @@
           <t>Ramirez Sanchez</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E290" t="n">
+        <v/>
       </c>
     </row>
     <row r="291">
@@ -6817,10 +6259,8 @@
           <t>Hernandez</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E291" t="n">
+        <v/>
       </c>
     </row>
     <row r="292">
@@ -6839,10 +6279,8 @@
           <t>Castano</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E292" t="n">
+        <v/>
       </c>
     </row>
     <row r="293">
@@ -6861,10 +6299,8 @@
           <t>Suarez Triana</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E293" t="n">
+        <v/>
       </c>
     </row>
     <row r="294">
@@ -6883,10 +6319,8 @@
           <t>Ocampo</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E294" t="n">
+        <v/>
       </c>
     </row>
     <row r="295">
@@ -6905,10 +6339,8 @@
           <t>Ramírez Villegas</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E295" t="n">
+        <v/>
       </c>
     </row>
     <row r="296">
@@ -6927,10 +6359,8 @@
           <t>Barrios</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E296" t="n">
+        <v/>
       </c>
     </row>
     <row r="297">
@@ -6949,10 +6379,8 @@
           <t>Sarasa</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E297" t="n">
+        <v/>
       </c>
     </row>
     <row r="298">
@@ -6971,10 +6399,8 @@
           <t>Meneses</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E298" t="n">
+        <v/>
       </c>
     </row>
     <row r="299">
@@ -6993,10 +6419,8 @@
           <t>Escobar Franco</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E299" t="n">
+        <v/>
       </c>
     </row>
     <row r="300">
@@ -7015,10 +6439,8 @@
           <t>Naranjo Pizano</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E300" t="n">
+        <v/>
       </c>
     </row>
     <row r="301">
@@ -7037,10 +6459,8 @@
           <t>Arboleda</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E301" t="n">
+        <v/>
       </c>
     </row>
     <row r="302">
@@ -7059,10 +6479,8 @@
           <t>Flórez</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E302" t="n">
+        <v/>
       </c>
     </row>
     <row r="303">
@@ -7081,10 +6499,8 @@
           <t>Barrera</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E303" t="n">
+        <v/>
       </c>
     </row>
     <row r="304">
@@ -7103,10 +6519,8 @@
           <t>Alba</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E304" t="n">
+        <v/>
       </c>
     </row>
     <row r="305">
@@ -7125,10 +6539,8 @@
           <t>Yepes Tabares</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E305" t="n">
+        <v/>
       </c>
     </row>
     <row r="306">
@@ -7147,10 +6559,8 @@
           <t>Álvarez Restrepo</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E306" t="n">
+        <v/>
       </c>
     </row>
     <row r="307">
@@ -7169,10 +6579,8 @@
           <t>Payares</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E307" t="n">
+        <v/>
       </c>
     </row>
     <row r="308">
@@ -7191,10 +6599,8 @@
           <t>Jaramillo</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E308" t="n">
+        <v/>
       </c>
     </row>
     <row r="309">
@@ -7213,10 +6619,8 @@
           <t>Munera Rua</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E309" t="n">
+        <v/>
       </c>
     </row>
     <row r="310">
@@ -7235,10 +6639,8 @@
           <t>Alvarez Fernandez</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E310" t="n">
+        <v/>
       </c>
     </row>
     <row r="311">
@@ -7257,10 +6659,8 @@
           <t>Bedoya</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E311" t="n">
+        <v/>
       </c>
     </row>
     <row r="312">
@@ -7279,10 +6679,8 @@
           <t>Florez Garcia</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E312" t="n">
+        <v/>
       </c>
     </row>
     <row r="313">
@@ -7301,10 +6699,8 @@
           <t>Marchese</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E313" t="n">
+        <v/>
       </c>
     </row>
     <row r="314">
@@ -7323,10 +6719,8 @@
           <t>Prueba Aguilar</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E314" t="n">
+        <v/>
       </c>
     </row>
     <row r="315">
@@ -7345,10 +6739,8 @@
           <t>Pabon</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E315" t="n">
+        <v/>
       </c>
     </row>
     <row r="316">
@@ -7367,10 +6759,8 @@
           <t>Or.mm</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E316" t="n">
+        <v/>
       </c>
     </row>
     <row r="317">
@@ -7389,10 +6779,8 @@
           <t>De La Hoz</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E317" t="n">
+        <v/>
       </c>
     </row>
     <row r="318">
@@ -7411,10 +6799,8 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E318" t="n">
+        <v/>
       </c>
     </row>
     <row r="319">
@@ -7433,10 +6819,8 @@
           <t>Portilla Araujo</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E319" t="n">
+        <v/>
       </c>
     </row>
     <row r="320">
@@ -7455,10 +6839,8 @@
           <t>Arango</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E320" t="n">
+        <v/>
       </c>
     </row>
     <row r="321">
@@ -7477,10 +6859,8 @@
           <t>González</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>VIVE LIVING</t>
-        </is>
+      <c r="E321" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/output/customers_Vive_Living.xlsx
+++ b/output/customers_Vive_Living.xlsx
@@ -459,8 +459,10 @@
           <t>Berrios Olivera</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -479,8 +481,10 @@
           <t>Arango Ossa</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -499,8 +503,10 @@
           <t>Gaviria Hernandez</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -519,8 +525,10 @@
           <t>Garzón</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -539,8 +547,10 @@
           <t>Otero</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -559,8 +569,10 @@
           <t>Ramirez Díaz</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -579,8 +591,10 @@
           <t>Molina</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -599,8 +613,10 @@
           <t>Medina</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -619,8 +635,10 @@
           <t>Ome</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -639,8 +657,10 @@
           <t>Ramirez Atehortúa</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -659,8 +679,10 @@
           <t>Moreno</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -679,8 +701,10 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -699,8 +723,10 @@
           <t>Bocanegra</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -719,8 +745,10 @@
           <t>Hincapie</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -739,8 +767,10 @@
           <t>Abdala Gonzalez</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -759,8 +789,10 @@
           <t>Álvarez</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -779,8 +811,10 @@
           <t>Alcalá Quijano</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -799,8 +833,10 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -819,8 +855,10 @@
           <t>Malaver</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -839,8 +877,10 @@
           <t>Cadavid</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -859,8 +899,10 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -879,8 +921,10 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -899,8 +943,10 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -919,8 +965,10 @@
           <t>Ayala Lopez</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -939,8 +987,10 @@
           <t>Naranjo</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -959,8 +1009,10 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -979,8 +1031,10 @@
           <t>Longa</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -999,8 +1053,10 @@
           <t>Manco Tobon</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1019,8 +1075,10 @@
           <t>Bernal</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1039,8 +1097,10 @@
           <t>Mora</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1059,8 +1119,10 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1101,8 +1163,10 @@
           <t>Morales</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1121,8 +1185,10 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1141,8 +1207,10 @@
           <t>Marcela</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1161,8 +1229,10 @@
           <t>Duran</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1181,8 +1251,10 @@
           <t>Perez</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1201,8 +1273,10 @@
           <t>Mosquera Vanegas</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1221,8 +1295,10 @@
           <t>Parra</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1241,8 +1317,10 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1261,8 +1339,10 @@
           <t>Espinosa</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1281,8 +1361,10 @@
           <t>Mendez</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1301,8 +1383,10 @@
           <t>Villa Villegas</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1321,8 +1405,10 @@
           <t>Calle</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1341,8 +1427,10 @@
           <t>Gomez</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1361,8 +1449,10 @@
           <t>Barrera</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1381,8 +1471,10 @@
           <t>Londoño Castaño</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1401,8 +1493,10 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1421,8 +1515,10 @@
           <t>Garcia</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1441,8 +1537,10 @@
           <t>Zambrano</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1461,8 +1559,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1481,8 +1581,10 @@
           <t>Cardenas Cruz</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1501,8 +1603,10 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1521,8 +1625,10 @@
           <t>Montaño Parra</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1541,8 +1647,10 @@
           <t>Arboleda</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1583,8 +1691,10 @@
           <t>Lopera Velez</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1603,8 +1713,10 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1623,8 +1735,10 @@
           <t>Herrera</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1643,8 +1757,10 @@
           <t>Cano</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1663,8 +1779,10 @@
           <t>Mejia</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1705,8 +1823,10 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1725,8 +1845,10 @@
           <t>Castano</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1745,8 +1867,10 @@
           <t>Duque</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1765,8 +1889,10 @@
           <t>Freydell</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1785,8 +1911,10 @@
           <t>Serna Blandon</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1805,8 +1933,10 @@
           <t>Lasso Arias</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1825,8 +1955,10 @@
           <t>Chico Torres</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1845,8 +1977,10 @@
           <t>Gutierrez Rivas</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1865,8 +1999,10 @@
           <t>Villegas</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1885,8 +2021,10 @@
           <t>Bermudez</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1905,8 +2043,10 @@
           <t>Roldán Botero</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1925,8 +2065,10 @@
           <t>Jiménez</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1945,8 +2087,10 @@
           <t>Acosta</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1965,8 +2109,10 @@
           <t>Vélez</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1985,8 +2131,10 @@
           <t>Escobar Vélez</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2005,8 +2153,10 @@
           <t>Patiño</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2025,8 +2175,10 @@
           <t>Becerra</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2045,8 +2197,10 @@
           <t>Montoya Hoyos</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2065,8 +2219,10 @@
           <t>Sánchez</t>
         </is>
       </c>
-      <c r="E82" t="n">
-        <v/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2085,8 +2241,10 @@
           <t>Gaviria</t>
         </is>
       </c>
-      <c r="E83" t="n">
-        <v/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2105,8 +2263,10 @@
           <t>Matiz</t>
         </is>
       </c>
-      <c r="E84" t="n">
-        <v/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -2125,8 +2285,10 @@
           <t>Cortes Santos</t>
         </is>
       </c>
-      <c r="E85" t="n">
-        <v/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2145,8 +2307,10 @@
           <t>Vargas</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2165,8 +2329,10 @@
           <t>Hincapi</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2185,8 +2351,10 @@
           <t>Segura</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2205,8 +2373,10 @@
           <t>Daza</t>
         </is>
       </c>
-      <c r="E89" t="n">
-        <v/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2225,8 +2395,10 @@
           <t>Patiño</t>
         </is>
       </c>
-      <c r="E90" t="n">
-        <v/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2245,8 +2417,10 @@
           <t>Moreno</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2265,8 +2439,10 @@
           <t>Fajardo</t>
         </is>
       </c>
-      <c r="E92" t="n">
-        <v/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -2285,8 +2461,10 @@
           <t>Mejia Gomez</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2305,8 +2483,10 @@
           <t>Espinal</t>
         </is>
       </c>
-      <c r="E94" t="n">
-        <v/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2325,8 +2505,10 @@
           <t>Vlez</t>
         </is>
       </c>
-      <c r="E95" t="n">
-        <v/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2345,8 +2527,10 @@
           <t>Lovera</t>
         </is>
       </c>
-      <c r="E96" t="n">
-        <v/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2365,8 +2549,10 @@
           <t>Orozco</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2385,8 +2571,10 @@
           <t>Franco</t>
         </is>
       </c>
-      <c r="E98" t="n">
-        <v/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -2405,8 +2593,10 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E99" t="n">
-        <v/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -2425,8 +2615,10 @@
           <t>Herrera Herrera</t>
         </is>
       </c>
-      <c r="E100" t="n">
-        <v/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -2445,8 +2637,10 @@
           <t>Salazar Arredondo</t>
         </is>
       </c>
-      <c r="E101" t="n">
-        <v/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -2465,8 +2659,10 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E102" t="n">
-        <v/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -2485,8 +2681,10 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E103" t="n">
-        <v/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2505,8 +2703,10 @@
           <t>Marin Osorio</t>
         </is>
       </c>
-      <c r="E104" t="n">
-        <v/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -2525,8 +2725,10 @@
           <t>Vélez</t>
         </is>
       </c>
-      <c r="E105" t="n">
-        <v/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2545,8 +2747,10 @@
           <t>Saldarriaga</t>
         </is>
       </c>
-      <c r="E106" t="n">
-        <v/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -2565,8 +2769,10 @@
           <t>Gil</t>
         </is>
       </c>
-      <c r="E107" t="n">
-        <v/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -2585,8 +2791,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E108" t="n">
-        <v/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -2605,8 +2813,10 @@
           <t>Gómez Fernández</t>
         </is>
       </c>
-      <c r="E109" t="n">
-        <v/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -2625,8 +2835,10 @@
           <t>Alvarez</t>
         </is>
       </c>
-      <c r="E110" t="n">
-        <v/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -2645,8 +2857,10 @@
           <t>Quintero</t>
         </is>
       </c>
-      <c r="E111" t="n">
-        <v/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -2665,8 +2879,10 @@
           <t>Martinez</t>
         </is>
       </c>
-      <c r="E112" t="n">
-        <v/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -2685,8 +2901,10 @@
           <t>Villa</t>
         </is>
       </c>
-      <c r="E113" t="n">
-        <v/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -2705,8 +2923,10 @@
           <t>Montoya</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -2725,8 +2945,10 @@
           <t>Mueses</t>
         </is>
       </c>
-      <c r="E115" t="n">
-        <v/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -2745,8 +2967,10 @@
           <t>Echavarria</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -2765,8 +2989,10 @@
           <t>Turpin Martinez</t>
         </is>
       </c>
-      <c r="E117" t="n">
-        <v/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -2785,8 +3011,10 @@
           <t>Espinosa Montoya</t>
         </is>
       </c>
-      <c r="E118" t="n">
-        <v/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -2805,8 +3033,10 @@
           <t>Tobías</t>
         </is>
       </c>
-      <c r="E119" t="n">
-        <v/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -2825,8 +3055,10 @@
           <t>Botia</t>
         </is>
       </c>
-      <c r="E120" t="n">
-        <v/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -2845,8 +3077,10 @@
           <t>Quiintero</t>
         </is>
       </c>
-      <c r="E121" t="n">
-        <v/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -2865,8 +3099,10 @@
           <t>Mejia Restrepo</t>
         </is>
       </c>
-      <c r="E122" t="n">
-        <v/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -2885,8 +3121,10 @@
           <t>Gutierrez Giraldo</t>
         </is>
       </c>
-      <c r="E123" t="n">
-        <v/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -2905,8 +3143,10 @@
           <t>Hernández Camargo</t>
         </is>
       </c>
-      <c r="E124" t="n">
-        <v/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -2925,8 +3165,10 @@
           <t>Restrepo Correa</t>
         </is>
       </c>
-      <c r="E125" t="n">
-        <v/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -2945,8 +3187,10 @@
           <t>Uribe</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -2965,8 +3209,10 @@
           <t>Zuluaga Salazar</t>
         </is>
       </c>
-      <c r="E127" t="n">
-        <v/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -2985,8 +3231,10 @@
           <t>Gutierrez Garcia</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -3005,8 +3253,10 @@
           <t>Pelaez</t>
         </is>
       </c>
-      <c r="E129" t="n">
-        <v/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -3025,8 +3275,10 @@
           <t>Pérez</t>
         </is>
       </c>
-      <c r="E130" t="n">
-        <v/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -3045,8 +3297,10 @@
           <t>Gómez</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -3065,8 +3319,10 @@
           <t>Rincón Castaño</t>
         </is>
       </c>
-      <c r="E132" t="n">
-        <v/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -3085,8 +3341,10 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="E133" t="n">
-        <v/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -3105,8 +3363,10 @@
           <t>Palacio Agudelo</t>
         </is>
       </c>
-      <c r="E134" t="n">
-        <v/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -3147,8 +3407,10 @@
           <t>Agámez Marchena</t>
         </is>
       </c>
-      <c r="E136" t="n">
-        <v/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -3167,8 +3429,10 @@
           <t>Castro</t>
         </is>
       </c>
-      <c r="E137" t="n">
-        <v/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -3187,8 +3451,10 @@
           <t>Gallego</t>
         </is>
       </c>
-      <c r="E138" t="n">
-        <v/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -3207,8 +3473,10 @@
           <t>Gutierrez Fonseca</t>
         </is>
       </c>
-      <c r="E139" t="n">
-        <v/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -3227,8 +3495,10 @@
           <t>Urueta</t>
         </is>
       </c>
-      <c r="E140" t="n">
-        <v/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -3247,8 +3517,10 @@
           <t>Grajales Rua</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -3267,8 +3539,10 @@
           <t>Hernandez</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -3287,8 +3561,10 @@
           <t>Cecilia Restrepo Alvarez</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -3307,8 +3583,10 @@
           <t>Rodriguez Zamora</t>
         </is>
       </c>
-      <c r="E144" t="n">
-        <v/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -3327,8 +3605,10 @@
           <t>Pantoja Santacruz</t>
         </is>
       </c>
-      <c r="E145" t="n">
-        <v/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -3347,8 +3627,10 @@
           <t>Trujillo</t>
         </is>
       </c>
-      <c r="E146" t="n">
-        <v/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -3367,8 +3649,10 @@
           <t>Garciagarcia</t>
         </is>
       </c>
-      <c r="E147" t="n">
-        <v/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -3387,8 +3671,10 @@
           <t>Velez Alvarez</t>
         </is>
       </c>
-      <c r="E148" t="n">
-        <v/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -3407,8 +3693,10 @@
           <t>Loboa Caicedo</t>
         </is>
       </c>
-      <c r="E149" t="n">
-        <v/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -3427,8 +3715,10 @@
           <t>Gómez Escorcia</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -3447,8 +3737,10 @@
           <t>V</t>
         </is>
       </c>
-      <c r="E151" t="n">
-        <v/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -3467,8 +3759,10 @@
           <t>Hoyos Gomez</t>
         </is>
       </c>
-      <c r="E152" t="n">
-        <v/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -3487,8 +3781,10 @@
           <t>Gonzalez</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -3507,8 +3803,10 @@
           <t>Rendon</t>
         </is>
       </c>
-      <c r="E154" t="n">
-        <v/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -3527,8 +3825,10 @@
           <t>Mario Pérez</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -3547,8 +3847,10 @@
           <t>Suescún Bedoya</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -3567,8 +3869,10 @@
           <t>Cardeño Rengifo</t>
         </is>
       </c>
-      <c r="E157" t="n">
-        <v/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -3587,8 +3891,10 @@
           <t>Contreras</t>
         </is>
       </c>
-      <c r="E158" t="n">
-        <v/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -3607,8 +3913,10 @@
           <t>Bohorquez Orozco</t>
         </is>
       </c>
-      <c r="E159" t="n">
-        <v/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -3627,8 +3935,10 @@
           <t>Hernández Castro</t>
         </is>
       </c>
-      <c r="E160" t="n">
-        <v/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -3647,8 +3957,10 @@
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="E161" t="n">
-        <v/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -3667,8 +3979,10 @@
           <t>D. Arboleda</t>
         </is>
       </c>
-      <c r="E162" t="n">
-        <v/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -3687,8 +4001,10 @@
           <t>Zuluaga</t>
         </is>
       </c>
-      <c r="E163" t="n">
-        <v/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -3707,8 +4023,10 @@
           <t>Gallego Diaz</t>
         </is>
       </c>
-      <c r="E164" t="n">
-        <v/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -3727,8 +4045,10 @@
           <t>Uribe</t>
         </is>
       </c>
-      <c r="E165" t="n">
-        <v/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -3747,8 +4067,10 @@
           <t>Henao</t>
         </is>
       </c>
-      <c r="E166" t="n">
-        <v/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -3767,8 +4089,10 @@
           <t>Pnl</t>
         </is>
       </c>
-      <c r="E167" t="n">
-        <v/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -3787,8 +4111,10 @@
           <t>Mesa</t>
         </is>
       </c>
-      <c r="E168" t="n">
-        <v/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -3829,8 +4155,10 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E170" t="n">
-        <v/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -3849,8 +4177,10 @@
           <t>Rubin</t>
         </is>
       </c>
-      <c r="E171" t="n">
-        <v/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -3869,8 +4199,10 @@
           <t>Uriana</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -3911,8 +4243,10 @@
           <t>Pareja</t>
         </is>
       </c>
-      <c r="E174" t="n">
-        <v/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -3931,8 +4265,10 @@
           <t>Molina</t>
         </is>
       </c>
-      <c r="E175" t="n">
-        <v/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -3951,8 +4287,10 @@
           <t>Hoyos</t>
         </is>
       </c>
-      <c r="E176" t="n">
-        <v/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -3971,8 +4309,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E177" t="n">
-        <v/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -3991,8 +4331,10 @@
           <t>Escobar</t>
         </is>
       </c>
-      <c r="E178" t="n">
-        <v/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -4011,8 +4353,10 @@
           <t>Rua Penagos</t>
         </is>
       </c>
-      <c r="E179" t="n">
-        <v/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -4031,8 +4375,10 @@
           <t>Almanza</t>
         </is>
       </c>
-      <c r="E180" t="n">
-        <v/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -4051,8 +4397,10 @@
           <t>Velasquez Giraldo</t>
         </is>
       </c>
-      <c r="E181" t="n">
-        <v/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -4093,8 +4441,10 @@
           <t>De La Hoz Osorio</t>
         </is>
       </c>
-      <c r="E183" t="n">
-        <v/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -4113,8 +4463,10 @@
           <t>Pineda Arango</t>
         </is>
       </c>
-      <c r="E184" t="n">
-        <v/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -4133,8 +4485,10 @@
           <t>Hinestrosa</t>
         </is>
       </c>
-      <c r="E185" t="n">
-        <v/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -4175,8 +4529,10 @@
           <t>Ruiz Galeano</t>
         </is>
       </c>
-      <c r="E187" t="n">
-        <v/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -4195,8 +4551,10 @@
           <t>Delgado Restrepo</t>
         </is>
       </c>
-      <c r="E188" t="n">
-        <v/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -4215,8 +4573,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E189" t="n">
-        <v/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -4235,8 +4595,10 @@
           <t>Zanoja</t>
         </is>
       </c>
-      <c r="E190" t="n">
-        <v/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -4255,8 +4617,10 @@
           <t>Cifuentes Gonzalez</t>
         </is>
       </c>
-      <c r="E191" t="n">
-        <v/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -4275,8 +4639,10 @@
           <t>Lozano</t>
         </is>
       </c>
-      <c r="E192" t="n">
-        <v/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -4295,8 +4661,10 @@
           <t>Guzmán Gomez</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -4315,8 +4683,10 @@
           <t>Salgdo</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -4335,8 +4705,10 @@
           <t>Mesa Martínez</t>
         </is>
       </c>
-      <c r="E195" t="n">
-        <v/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -4355,8 +4727,10 @@
           <t>Rodríguez</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -4375,8 +4749,10 @@
           <t>Soto Aristizabal</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -4395,8 +4771,10 @@
           <t>Velasquez</t>
         </is>
       </c>
-      <c r="E198" t="n">
-        <v/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -4415,8 +4793,10 @@
           <t>Agudelo Vélez</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -4435,8 +4815,10 @@
           <t>León Cruz</t>
         </is>
       </c>
-      <c r="E200" t="n">
-        <v/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -4455,8 +4837,10 @@
           <t>Patiño Avendaño</t>
         </is>
       </c>
-      <c r="E201" t="n">
-        <v/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -4475,8 +4859,10 @@
           <t>Martínez Giraldo</t>
         </is>
       </c>
-      <c r="E202" t="n">
-        <v/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -4495,8 +4881,10 @@
           <t>Calle Echavarria</t>
         </is>
       </c>
-      <c r="E203" t="n">
-        <v/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -4515,8 +4903,10 @@
           <t>Rivas Durango</t>
         </is>
       </c>
-      <c r="E204" t="n">
-        <v/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -4535,8 +4925,10 @@
           <t>Cabrera</t>
         </is>
       </c>
-      <c r="E205" t="n">
-        <v/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -4555,8 +4947,10 @@
           <t>Parada</t>
         </is>
       </c>
-      <c r="E206" t="n">
-        <v/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -4575,8 +4969,10 @@
           <t>Fernández Echeverri</t>
         </is>
       </c>
-      <c r="E207" t="n">
-        <v/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -4595,8 +4991,10 @@
           <t>Cicery</t>
         </is>
       </c>
-      <c r="E208" t="n">
-        <v/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -4615,8 +5013,10 @@
           <t>Jimenez Castañeda</t>
         </is>
       </c>
-      <c r="E209" t="n">
-        <v/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -4635,8 +5035,10 @@
           <t>Salamanca Castro</t>
         </is>
       </c>
-      <c r="E210" t="n">
-        <v/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -4655,8 +5057,10 @@
           <t>Sanchez Alvarez</t>
         </is>
       </c>
-      <c r="E211" t="n">
-        <v/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -4675,8 +5079,10 @@
           <t>Delgado</t>
         </is>
       </c>
-      <c r="E212" t="n">
-        <v/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -4695,8 +5101,10 @@
           <t>Rojas Guevara</t>
         </is>
       </c>
-      <c r="E213" t="n">
-        <v/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -4715,8 +5123,10 @@
           <t>Martinez</t>
         </is>
       </c>
-      <c r="E214" t="n">
-        <v/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -4735,8 +5145,10 @@
           <t>Jiménez</t>
         </is>
       </c>
-      <c r="E215" t="n">
-        <v/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -4755,8 +5167,10 @@
           <t>Arias Perez</t>
         </is>
       </c>
-      <c r="E216" t="n">
-        <v/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -4775,8 +5189,10 @@
           <t>Salinas</t>
         </is>
       </c>
-      <c r="E217" t="n">
-        <v/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -4795,8 +5211,10 @@
           <t>Aristizabal</t>
         </is>
       </c>
-      <c r="E218" t="n">
-        <v/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -4815,8 +5233,10 @@
           <t>Serna</t>
         </is>
       </c>
-      <c r="E219" t="n">
-        <v/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -4835,8 +5255,10 @@
           <t>Andres Cardona</t>
         </is>
       </c>
-      <c r="E220" t="n">
-        <v/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -4855,8 +5277,10 @@
           <t>Callejas Varela</t>
         </is>
       </c>
-      <c r="E221" t="n">
-        <v/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -4875,8 +5299,10 @@
           <t>Miranda</t>
         </is>
       </c>
-      <c r="E222" t="n">
-        <v/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -4895,8 +5321,10 @@
           <t>Florez Urrego</t>
         </is>
       </c>
-      <c r="E223" t="n">
-        <v/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -4915,8 +5343,10 @@
           <t>Cañón</t>
         </is>
       </c>
-      <c r="E224" t="n">
-        <v/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -4935,8 +5365,10 @@
           <t>Osorio Tamayo</t>
         </is>
       </c>
-      <c r="E225" t="n">
-        <v/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -4955,8 +5387,10 @@
           <t>Lopez</t>
         </is>
       </c>
-      <c r="E226" t="n">
-        <v/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -4975,8 +5409,10 @@
           <t>Ceballos</t>
         </is>
       </c>
-      <c r="E227" t="n">
-        <v/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -4995,8 +5431,10 @@
           <t>Cristancho</t>
         </is>
       </c>
-      <c r="E228" t="n">
-        <v/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -5015,8 +5453,10 @@
           <t>Arias</t>
         </is>
       </c>
-      <c r="E229" t="n">
-        <v/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -5035,8 +5475,10 @@
           <t>Arias Cadavid</t>
         </is>
       </c>
-      <c r="E230" t="n">
-        <v/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -5055,8 +5497,10 @@
           <t>Zuñiga</t>
         </is>
       </c>
-      <c r="E231" t="n">
-        <v/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -5075,8 +5519,10 @@
           <t>Cardona</t>
         </is>
       </c>
-      <c r="E232" t="n">
-        <v/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -5095,8 +5541,10 @@
           <t>Clavijo</t>
         </is>
       </c>
-      <c r="E233" t="n">
-        <v/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -5115,8 +5563,10 @@
           <t>Torres</t>
         </is>
       </c>
-      <c r="E234" t="n">
-        <v/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -5135,8 +5585,10 @@
           <t>Bohórquez</t>
         </is>
       </c>
-      <c r="E235" t="n">
-        <v/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -5155,8 +5607,10 @@
           <t>Sierra</t>
         </is>
       </c>
-      <c r="E236" t="n">
-        <v/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -5175,8 +5629,10 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E237" t="n">
-        <v/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -5195,8 +5651,10 @@
           <t>Salas</t>
         </is>
       </c>
-      <c r="E238" t="n">
-        <v/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -5215,8 +5673,10 @@
           <t>Franco</t>
         </is>
       </c>
-      <c r="E239" t="n">
-        <v/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -5235,8 +5695,10 @@
           <t>Garcia Rios</t>
         </is>
       </c>
-      <c r="E240" t="n">
-        <v/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -5255,8 +5717,10 @@
           <t>Cecilia Perez Pulgarin</t>
         </is>
       </c>
-      <c r="E241" t="n">
-        <v/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -5275,8 +5739,10 @@
           <t>Fabricio Concejal</t>
         </is>
       </c>
-      <c r="E242" t="n">
-        <v/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -5295,8 +5761,10 @@
           <t>Humana</t>
         </is>
       </c>
-      <c r="E243" t="n">
-        <v/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -5315,8 +5783,10 @@
           <t>Sucerquia</t>
         </is>
       </c>
-      <c r="E244" t="n">
-        <v/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -5335,8 +5805,10 @@
           <t>Cabrales</t>
         </is>
       </c>
-      <c r="E245" t="n">
-        <v/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -5355,8 +5827,10 @@
           <t>Pasos</t>
         </is>
       </c>
-      <c r="E246" t="n">
-        <v/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -5375,8 +5849,10 @@
           <t>González</t>
         </is>
       </c>
-      <c r="E247" t="n">
-        <v/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -5395,8 +5871,10 @@
           <t>Salas Araque</t>
         </is>
       </c>
-      <c r="E248" t="n">
-        <v/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -5415,8 +5893,10 @@
           <t>Chaparro</t>
         </is>
       </c>
-      <c r="E249" t="n">
-        <v/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -5435,8 +5915,10 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E250" t="n">
-        <v/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -5455,8 +5937,10 @@
           <t>Morales Cañón</t>
         </is>
       </c>
-      <c r="E251" t="n">
-        <v/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -5475,8 +5959,10 @@
           <t>Plazas Sanchez</t>
         </is>
       </c>
-      <c r="E252" t="n">
-        <v/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -5495,8 +5981,10 @@
           <t>Agudelo</t>
         </is>
       </c>
-      <c r="E253" t="n">
-        <v/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -5515,8 +6003,10 @@
           <t>Adolfo Santa</t>
         </is>
       </c>
-      <c r="E254" t="n">
-        <v/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -5535,8 +6025,10 @@
           <t>Medina</t>
         </is>
       </c>
-      <c r="E255" t="n">
-        <v/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -5555,8 +6047,10 @@
           <t>Puello</t>
         </is>
       </c>
-      <c r="E256" t="n">
-        <v/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -5575,8 +6069,10 @@
           <t>Gutiérrez</t>
         </is>
       </c>
-      <c r="E257" t="n">
-        <v/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -5595,8 +6091,10 @@
           <t>Castillo</t>
         </is>
       </c>
-      <c r="E258" t="n">
-        <v/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -5615,8 +6113,10 @@
           <t>Bedoya</t>
         </is>
       </c>
-      <c r="E259" t="n">
-        <v/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -5657,8 +6157,10 @@
           <t>Rudas</t>
         </is>
       </c>
-      <c r="E261" t="n">
-        <v/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -5677,8 +6179,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E262" t="n">
-        <v/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -5697,8 +6201,10 @@
           <t>Vallejo</t>
         </is>
       </c>
-      <c r="E263" t="n">
-        <v/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -5717,8 +6223,10 @@
           <t>Perez Sierra</t>
         </is>
       </c>
-      <c r="E264" t="n">
-        <v/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -5737,8 +6245,10 @@
           <t>Yepes</t>
         </is>
       </c>
-      <c r="E265" t="n">
-        <v/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -5757,8 +6267,10 @@
           <t>Pérez Uribe</t>
         </is>
       </c>
-      <c r="E266" t="n">
-        <v/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -5799,8 +6311,10 @@
           <t>Maya G</t>
         </is>
       </c>
-      <c r="E268" t="n">
-        <v/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -5819,8 +6333,10 @@
           <t>Rivera Caro</t>
         </is>
       </c>
-      <c r="E269" t="n">
-        <v/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -5839,8 +6355,10 @@
           <t>Zapata</t>
         </is>
       </c>
-      <c r="E270" t="n">
-        <v/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -5859,8 +6377,10 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E271" t="n">
-        <v/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -5879,8 +6399,10 @@
           <t>Sandoval</t>
         </is>
       </c>
-      <c r="E272" t="n">
-        <v/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -5899,8 +6421,10 @@
           <t>Rodriguez</t>
         </is>
       </c>
-      <c r="E273" t="n">
-        <v/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -5919,8 +6443,10 @@
           <t>Alexandra Grisales Vahos</t>
         </is>
       </c>
-      <c r="E274" t="n">
-        <v/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -5939,8 +6465,10 @@
           <t>Rhenals Garrido</t>
         </is>
       </c>
-      <c r="E275" t="n">
-        <v/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -5959,8 +6487,10 @@
           <t>Gaviria</t>
         </is>
       </c>
-      <c r="E276" t="n">
-        <v/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -5979,8 +6509,10 @@
           <t>Ángel</t>
         </is>
       </c>
-      <c r="E277" t="n">
-        <v/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -5999,8 +6531,10 @@
           <t>Ayala Lopez</t>
         </is>
       </c>
-      <c r="E278" t="n">
-        <v/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -6019,8 +6553,10 @@
           <t>Arango</t>
         </is>
       </c>
-      <c r="E279" t="n">
-        <v/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -6039,8 +6575,10 @@
           <t>Campos</t>
         </is>
       </c>
-      <c r="E280" t="n">
-        <v/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -6059,8 +6597,10 @@
           <t>Vásquez Rodriguez</t>
         </is>
       </c>
-      <c r="E281" t="n">
-        <v/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -6079,8 +6619,10 @@
           <t>Quintero Duque</t>
         </is>
       </c>
-      <c r="E282" t="n">
-        <v/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -6099,8 +6641,10 @@
           <t>Restrepo</t>
         </is>
       </c>
-      <c r="E283" t="n">
-        <v/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -6119,8 +6663,10 @@
           <t>Ramirez</t>
         </is>
       </c>
-      <c r="E284" t="n">
-        <v/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -6139,8 +6685,10 @@
           <t>Muñoz Valero</t>
         </is>
       </c>
-      <c r="E285" t="n">
-        <v/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -6159,8 +6707,10 @@
           <t>Cortes</t>
         </is>
       </c>
-      <c r="E286" t="n">
-        <v/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -6179,8 +6729,10 @@
           <t>Machado Román</t>
         </is>
       </c>
-      <c r="E287" t="n">
-        <v/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -6199,8 +6751,10 @@
           <t>Flórez</t>
         </is>
       </c>
-      <c r="E288" t="n">
-        <v/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -6219,8 +6773,10 @@
           <t>Palacio Montoya</t>
         </is>
       </c>
-      <c r="E289" t="n">
-        <v/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -6239,8 +6795,10 @@
           <t>Ramirez Sanchez</t>
         </is>
       </c>
-      <c r="E290" t="n">
-        <v/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -6259,8 +6817,10 @@
           <t>Hernandez</t>
         </is>
       </c>
-      <c r="E291" t="n">
-        <v/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -6279,8 +6839,10 @@
           <t>Castano</t>
         </is>
       </c>
-      <c r="E292" t="n">
-        <v/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -6299,8 +6861,10 @@
           <t>Suarez Triana</t>
         </is>
       </c>
-      <c r="E293" t="n">
-        <v/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -6319,8 +6883,10 @@
           <t>Ocampo</t>
         </is>
       </c>
-      <c r="E294" t="n">
-        <v/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -6339,8 +6905,10 @@
           <t>Ramírez Villegas</t>
         </is>
       </c>
-      <c r="E295" t="n">
-        <v/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -6359,8 +6927,10 @@
           <t>Barrios</t>
         </is>
       </c>
-      <c r="E296" t="n">
-        <v/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -6379,8 +6949,10 @@
           <t>Sarasa</t>
         </is>
       </c>
-      <c r="E297" t="n">
-        <v/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -6399,8 +6971,10 @@
           <t>Meneses</t>
         </is>
       </c>
-      <c r="E298" t="n">
-        <v/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -6419,8 +6993,10 @@
           <t>Escobar Franco</t>
         </is>
       </c>
-      <c r="E299" t="n">
-        <v/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -6439,8 +7015,10 @@
           <t>Naranjo Pizano</t>
         </is>
       </c>
-      <c r="E300" t="n">
-        <v/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -6459,8 +7037,10 @@
           <t>Arboleda</t>
         </is>
       </c>
-      <c r="E301" t="n">
-        <v/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -6479,8 +7059,10 @@
           <t>Flórez</t>
         </is>
       </c>
-      <c r="E302" t="n">
-        <v/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -6499,8 +7081,10 @@
           <t>Barrera</t>
         </is>
       </c>
-      <c r="E303" t="n">
-        <v/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -6519,8 +7103,10 @@
           <t>Alba</t>
         </is>
       </c>
-      <c r="E304" t="n">
-        <v/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -6539,8 +7125,10 @@
           <t>Yepes Tabares</t>
         </is>
       </c>
-      <c r="E305" t="n">
-        <v/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -6559,8 +7147,10 @@
           <t>Álvarez Restrepo</t>
         </is>
       </c>
-      <c r="E306" t="n">
-        <v/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -6579,8 +7169,10 @@
           <t>Payares</t>
         </is>
       </c>
-      <c r="E307" t="n">
-        <v/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -6599,8 +7191,10 @@
           <t>Jaramillo</t>
         </is>
       </c>
-      <c r="E308" t="n">
-        <v/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -6619,8 +7213,10 @@
           <t>Munera Rua</t>
         </is>
       </c>
-      <c r="E309" t="n">
-        <v/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -6639,8 +7235,10 @@
           <t>Alvarez Fernandez</t>
         </is>
       </c>
-      <c r="E310" t="n">
-        <v/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -6659,8 +7257,10 @@
           <t>Bedoya</t>
         </is>
       </c>
-      <c r="E311" t="n">
-        <v/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -6679,8 +7279,10 @@
           <t>Florez Garcia</t>
         </is>
       </c>
-      <c r="E312" t="n">
-        <v/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -6699,8 +7301,10 @@
           <t>Marchese</t>
         </is>
       </c>
-      <c r="E313" t="n">
-        <v/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -6719,8 +7323,10 @@
           <t>Prueba Aguilar</t>
         </is>
       </c>
-      <c r="E314" t="n">
-        <v/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -6739,8 +7345,10 @@
           <t>Pabon</t>
         </is>
       </c>
-      <c r="E315" t="n">
-        <v/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -6759,8 +7367,10 @@
           <t>Or.mm</t>
         </is>
       </c>
-      <c r="E316" t="n">
-        <v/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -6779,8 +7389,10 @@
           <t>De La Hoz</t>
         </is>
       </c>
-      <c r="E317" t="n">
-        <v/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -6799,8 +7411,10 @@
           <t>Rios</t>
         </is>
       </c>
-      <c r="E318" t="n">
-        <v/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -6819,8 +7433,10 @@
           <t>Portilla Araujo</t>
         </is>
       </c>
-      <c r="E319" t="n">
-        <v/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -6839,8 +7455,10 @@
           <t>Arango</t>
         </is>
       </c>
-      <c r="E320" t="n">
-        <v/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -6859,8 +7477,10 @@
           <t>González</t>
         </is>
       </c>
-      <c r="E321" t="n">
-        <v/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
       </c>
     </row>
   </sheetData>
